--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-10-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60b3ee8e5+80021]
-	GetHandleVerifier [0x0x7ff60b3ee940+80112]
-	(No symbol) [0x0x7ff60b17060f]
-	(No symbol) [0x0x7ff60b1c8854]
-	(No symbol) [0x0x7ff60b1c8b1c]
-	(No symbol) [0x0x7ff60b21c927]
-	(No symbol) [0x0x7ff60b1f126f]
-	(No symbol) [0x0x7ff60b21968a]
-	(No symbol) [0x0x7ff60b1f1003]
-	(No symbol) [0x0x7ff60b1b95d1]
-	(No symbol) [0x0x7ff60b1ba3f3]
-	GetHandleVerifier [0x0x7ff60b6adc7d+2960429]
-	GetHandleVerifier [0x0x7ff60b6a7f3a+2936554]
-	GetHandleVerifier [0x0x7ff60b6c8977+3070247]
-	GetHandleVerifier [0x0x7ff60b4083ce+185214]
-	GetHandleVerifier [0x0x7ff60b40fe1f+216527]
-	GetHandleVerifier [0x0x7ff60b3f7b24+117460]
-	GetHandleVerifier [0x0x7ff60b3f7cdf+117903]
-	GetHandleVerifier [0x0x7ff60b3ddbb8+11112]
+	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
+	GetHandleVerifier [0x0x7ff7928ee940+80112]
+	(No symbol) [0x0x7ff79267060f]
+	(No symbol) [0x0x7ff7926c8854]
+	(No symbol) [0x0x7ff7926c8b1c]
+	(No symbol) [0x0x7ff79271c927]
+	(No symbol) [0x0x7ff7926f126f]
+	(No symbol) [0x0x7ff79271968a]
+	(No symbol) [0x0x7ff7926f1003]
+	(No symbol) [0x0x7ff7926b95d1]
+	(No symbol) [0x0x7ff7926ba3f3]
+	GetHandleVerifier [0x0x7ff792badc7d+2960429]
+	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
+	GetHandleVerifier [0x0x7ff792bc8977+3070247]
+	GetHandleVerifier [0x0x7ff7929083ce+185214]
+	GetHandleVerifier [0x0x7ff79290fe1f+216527]
+	GetHandleVerifier [0x0x7ff7928f7b24+117460]
+	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
+	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-10-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -589,27 +589,27 @@
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -632,7 +632,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -710,27 +710,27 @@
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -753,7 +753,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -831,27 +831,27 @@
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -874,7 +874,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -952,27 +952,27 @@
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -995,7 +995,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1073,27 +1073,27 @@
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1194,27 +1194,27 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1315,27 +1315,27 @@
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1436,27 +1436,27 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>£29.33</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1557,27 +1557,27 @@
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1678,27 +1678,27 @@
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1799,27 +1799,27 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1920,27 +1920,27 @@
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2041,27 +2041,27 @@
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>£717.24</t>
+          <t>£59.77</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2162,27 +2162,27 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>£717.6</t>
+          <t>£59.8</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2283,27 +2283,27 @@
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2501,27 +2501,27 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>£1073.28</t>
+          <t>£89.44</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2622,27 +2622,27 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2743,27 +2743,27 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2864,27 +2864,27 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2985,27 +2985,27 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3106,27 +3106,27 @@
       <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>£85.44</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3227,27 +3227,27 @@
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3348,27 +3348,27 @@
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3469,27 +3469,27 @@
       <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7928ee8e5+80021]
-	GetHandleVerifier [0x0x7ff7928ee940+80112]
-	(No symbol) [0x0x7ff79267060f]
-	(No symbol) [0x0x7ff7926c8854]
-	(No symbol) [0x0x7ff7926c8b1c]
-	(No symbol) [0x0x7ff79271c927]
-	(No symbol) [0x0x7ff7926f126f]
-	(No symbol) [0x0x7ff79271968a]
-	(No symbol) [0x0x7ff7926f1003]
-	(No symbol) [0x0x7ff7926b95d1]
-	(No symbol) [0x0x7ff7926ba3f3]
-	GetHandleVerifier [0x0x7ff792badc7d+2960429]
-	GetHandleVerifier [0x0x7ff792ba7f3a+2936554]
-	GetHandleVerifier [0x0x7ff792bc8977+3070247]
-	GetHandleVerifier [0x0x7ff7929083ce+185214]
-	GetHandleVerifier [0x0x7ff79290fe1f+216527]
-	GetHandleVerifier [0x0x7ff7928f7b24+117460]
-	GetHandleVerifier [0x0x7ff7928f7cdf+117903]
-	GetHandleVerifier [0x0x7ff7928ddbb8+11112]
+	GetHandleVerifier [0x0x7ff78d76e8e5+80021]
+	GetHandleVerifier [0x0x7ff78d76e940+80112]
+	(No symbol) [0x0x7ff78d4f060f]
+	(No symbol) [0x0x7ff78d548854]
+	(No symbol) [0x0x7ff78d548b1c]
+	(No symbol) [0x0x7ff78d59c927]
+	(No symbol) [0x0x7ff78d57126f]
+	(No symbol) [0x0x7ff78d59968a]
+	(No symbol) [0x0x7ff78d571003]
+	(No symbol) [0x0x7ff78d5395d1]
+	(No symbol) [0x0x7ff78d53a3f3]
+	GetHandleVerifier [0x0x7ff78da2dc7d+2960429]
+	GetHandleVerifier [0x0x7ff78da27f3a+2936554]
+	GetHandleVerifier [0x0x7ff78da48977+3070247]
+	GetHandleVerifier [0x0x7ff78d7883ce+185214]
+	GetHandleVerifier [0x0x7ff78d78fe1f+216527]
+	GetHandleVerifier [0x0x7ff78d777b24+117460]
+	GetHandleVerifier [0x0x7ff78d777cdf+117903]
+	GetHandleVerifier [0x0x7ff78d75dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
